--- a/Configs/GameConfig/Datas/fg/#RaidTrigger-突袭触发.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RaidTrigger-突袭触发.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>触发来源系统还没做:承接 Story ID(此前只有接口与自检);已接入 = none</t>
+          <t>接入这个触发来源的 Story ID(只作溯源,运行时不据此关闭触发;FG10-RAID-01 已接入 purification);一开始就有 = none</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
